--- a/Data/vampseq_data_for_qc/20260413_VAMPseq_protein_domains.xlsx
+++ b/Data/vampseq_data_for_qc/20260413_VAMPseq_protein_domains.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivan/Documents/GitHub/PillarProject_CAVA_Analysis/Data/vampseq_data_for_qc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DB4598-14E2-1743-81D1-A68C6F52D083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE8A012-7A7B-054F-90E9-1C2AF53382D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{A6890493-859D-7C4F-828F-3AE6747E5755}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="2" xr2:uid="{A6890493-859D-7C4F-828F-3AE6747E5755}"/>
   </bookViews>
   <sheets>
     <sheet name="F9" sheetId="1" r:id="rId1"/>
+    <sheet name="G6PD" sheetId="2" r:id="rId2"/>
+    <sheet name="TSC2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>domain</t>
   </si>
@@ -54,16 +56,35 @@
   </si>
   <si>
     <t>Domain</t>
+  </si>
+  <si>
+    <t>NAD Binding Domain</t>
+  </si>
+  <si>
+    <t>C-Terminal Domain</t>
+  </si>
+  <si>
+    <t>Tuberin</t>
+  </si>
+  <si>
+    <t>RapGap</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -89,8 +110,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,4 +497,90 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F2152D-0E7A-B748-999C-A93815330C91}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>35</v>
+      </c>
+      <c r="C2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>212</v>
+      </c>
+      <c r="C3">
+        <v>503</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A152A57-CCFA-8847-B023-F23878174CB2}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>550</v>
+      </c>
+      <c r="C2">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>1525</v>
+      </c>
+      <c r="C3">
+        <v>1800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/vampseq_data_for_qc/20260413_VAMPseq_protein_domains.xlsx
+++ b/Data/vampseq_data_for_qc/20260413_VAMPseq_protein_domains.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivan/Documents/GitHub/PillarProject_CAVA_Analysis/Data/vampseq_data_for_qc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE8A012-7A7B-054F-90E9-1C2AF53382D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1712B60C-5F20-F947-B08D-A87C638A1107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="2" xr2:uid="{A6890493-859D-7C4F-828F-3AE6747E5755}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{A6890493-859D-7C4F-828F-3AE6747E5755}"/>
   </bookViews>
   <sheets>
     <sheet name="F9" sheetId="1" r:id="rId1"/>
@@ -38,26 +38,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>domain</t>
   </si>
   <si>
-    <t>Really</t>
-  </si>
-  <si>
-    <t>Important</t>
-  </si>
-  <si>
     <t>start</t>
   </si>
   <si>
     <t>end</t>
   </si>
   <si>
-    <t>Domain</t>
-  </si>
-  <si>
     <t>NAD Binding Domain</t>
   </si>
   <si>
@@ -68,6 +59,18 @@
   </si>
   <si>
     <t>RapGap</t>
+  </si>
+  <si>
+    <t>DUF3384</t>
+  </si>
+  <si>
+    <t>Gla</t>
+  </si>
+  <si>
+    <t>EGF</t>
+  </si>
+  <si>
+    <t>Protease</t>
   </si>
 </sst>
 </file>
@@ -455,43 +458,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C2">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>324</v>
+        <v>97</v>
       </c>
       <c r="C3">
-        <v>375</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>425</v>
+        <v>227</v>
       </c>
       <c r="C4">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -509,15 +512,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>35</v>
@@ -528,7 +531,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>212</v>
@@ -544,7 +547,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A152A57-CCFA-8847-B023-F23878174CB2}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -552,32 +555,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C2">
-        <v>750</v>
+        <v>903</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>1525</v>
+        <v>1561</v>
       </c>
       <c r="C3">
-        <v>1800</v>
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>54</v>
+      </c>
+      <c r="C4">
+        <v>469</v>
       </c>
     </row>
   </sheetData>
